--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -10793,7 +10793,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区首开Long街</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>首开Long街南区室外一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京昌平区首开Long街</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>首开Long街南区室外一层中庭</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -11615,17 +11615,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11635,29 +11635,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11667,29 +11667,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
@@ -11711,17 +11711,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11731,29 +11731,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11763,29 +11763,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11795,29 +11795,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11827,29 +11827,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11871,17 +11871,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
@@ -11903,17 +11903,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
@@ -11967,17 +11967,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -12026,7 +12026,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -12036,12 +12036,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12058,7 +12058,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12186,22 +12186,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12218,7 +12218,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -12228,12 +12228,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12250,22 +12250,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -10793,7 +10793,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区首开Long街</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>首开Long街南区室外一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京东城区国瑞城</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10872,7 +10872,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>国瑞城一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京昌平区首开Long街</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>首开Long街南区室外一层中庭</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京东城区国瑞城</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>国瑞城一层中庭</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -11615,17 +11615,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11635,29 +11635,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11667,29 +11667,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11699,29 +11699,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
@@ -11770,22 +11770,22 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11795,29 +11795,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11827,29 +11827,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11859,29 +11859,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11891,29 +11891,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
@@ -12026,22 +12026,22 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12058,22 +12058,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12090,22 +12090,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12122,22 +12122,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12159,17 +12159,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12186,22 +12186,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12218,7 +12218,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -12228,12 +12228,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12255,17 +12255,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -10291,7 +10291,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃钱塘新能源体验中心</t>
+          <t>杭州广沃临平卫星店</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
+          <t>浙江省杭州市临平区新天路176号1幢103室</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃临平卫星店</t>
+          <t>杭州广沃钱塘新能源体验中心</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市临平区新天路176号1幢103室</t>
+          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -10793,7 +10793,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京东城区国瑞城</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>国瑞城一层中庭</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10872,7 +10872,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京东城区国瑞城</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>国瑞城一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -11610,22 +11610,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11635,29 +11635,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11667,29 +11667,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11699,29 +11699,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
@@ -11802,22 +11802,22 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11827,29 +11827,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11859,29 +11859,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -11930,22 +11930,22 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
@@ -11967,17 +11967,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
@@ -12026,22 +12026,22 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12090,22 +12090,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12122,22 +12122,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12154,22 +12154,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12191,17 +12191,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12218,22 +12218,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12250,22 +12250,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -10291,7 +10291,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃临平卫星店</t>
+          <t>杭州广沃钱塘新能源体验中心</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市临平区新天路176号1幢103室</t>
+          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃钱塘新能源体验中心</t>
+          <t>杭州广沃临平卫星店</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
+          <t>浙江省杭州市临平区新天路176号1幢103室</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -10793,7 +10793,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京东城区国瑞城</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>国瑞城一层中庭</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京东城区国瑞城</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>国瑞城一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10872,7 +10872,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区首开Long街</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>首开Long街南区室外一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京昌平区首开Long街</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>首开Long街南区室外一层中庭</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -11610,22 +11610,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11635,29 +11635,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11667,29 +11667,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11699,29 +11699,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11731,29 +11731,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11763,29 +11763,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11795,29 +11795,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
@@ -11866,22 +11866,22 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11891,29 +11891,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
@@ -11967,17 +11967,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
@@ -12026,22 +12026,22 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12058,22 +12058,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12090,22 +12090,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12122,22 +12122,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12154,22 +12154,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12186,22 +12186,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12218,22 +12218,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12250,22 +12250,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -10291,7 +10291,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃钱塘新能源体验中心</t>
+          <t>杭州广沃临平卫星店</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
+          <t>浙江省杭州市临平区新天路176号1幢103室</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃临平卫星店</t>
+          <t>杭州广沃钱塘新能源体验中心</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市临平区新天路176号1幢103室</t>
+          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -10793,7 +10793,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京东城区国瑞城</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>国瑞城一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京东城区国瑞城</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10872,7 +10872,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>国瑞城一层中庭</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -11610,22 +11610,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
@@ -11647,17 +11647,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
@@ -11679,17 +11679,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11699,29 +11699,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11731,29 +11731,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11763,29 +11763,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
@@ -11834,22 +11834,22 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11859,29 +11859,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
@@ -11903,17 +11903,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
@@ -11967,17 +11967,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -12122,22 +12122,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12186,7 +12186,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12218,7 +12218,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -12228,12 +12228,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12250,22 +12250,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -10291,7 +10291,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃临平卫星店</t>
+          <t>杭州广沃钱塘新能源体验中心</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市临平区新天路176号1幢103室</t>
+          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃钱塘新能源体验中心</t>
+          <t>杭州广沃临平卫星店</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
+          <t>浙江省杭州市临平区新天路176号1幢103室</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -10793,7 +10793,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京东城区国瑞城</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>国瑞城一层中庭</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京东城区国瑞城</t>
+          <t>小米汽车北京昌平区首开Long街</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10872,7 +10872,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>国瑞城一层中庭</t>
+          <t>首开Long街南区室外一层中庭</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区首开Long街</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>首开Long街南区室外一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -11610,22 +11610,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
@@ -11647,17 +11647,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11667,29 +11667,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11699,29 +11699,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11731,29 +11731,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
@@ -11775,17 +11775,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11795,29 +11795,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11827,29 +11827,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11859,29 +11859,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11891,29 +11891,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -11967,17 +11967,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
@@ -12026,22 +12026,22 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12058,22 +12058,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12090,22 +12090,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12127,17 +12127,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12186,22 +12186,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12218,22 +12218,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12250,22 +12250,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -10889,7 +10889,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -11610,22 +11610,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
@@ -11647,17 +11647,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11667,29 +11667,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
@@ -11711,17 +11711,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
@@ -11775,17 +11775,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11795,29 +11795,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11827,29 +11827,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11859,29 +11859,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11891,29 +11891,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11955,29 +11955,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
@@ -12026,7 +12026,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -12036,12 +12036,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12058,22 +12058,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12100,12 +12100,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12127,17 +12127,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12154,22 +12154,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12186,22 +12186,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12250,22 +12250,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -10793,7 +10793,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京东城区国瑞城</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>国瑞城一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京东城区国瑞城</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>国瑞城一层中庭</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区首开Long街</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10872,7 +10872,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>首开Long街南区室外一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京昌平区首开Long街</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>首开Long街南区室外一层中庭</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -11610,22 +11610,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
@@ -11679,17 +11679,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11699,29 +11699,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11731,29 +11731,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
@@ -11775,17 +11775,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
@@ -11834,22 +11834,22 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
@@ -11898,22 +11898,22 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
@@ -11962,22 +11962,22 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
@@ -12026,7 +12026,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -12036,12 +12036,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12058,22 +12058,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12090,22 +12090,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12154,22 +12154,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12223,17 +12223,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12250,22 +12250,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -10291,7 +10291,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃钱塘新能源体验中心</t>
+          <t>杭州广沃临平卫星店</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
+          <t>浙江省杭州市临平区新天路176号1幢103室</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃临平卫星店</t>
+          <t>杭州广沃钱塘新能源体验中心</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市临平区新天路176号1幢103室</t>
+          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10872,7 +10872,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -11610,22 +11610,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11635,29 +11635,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
@@ -11679,17 +11679,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11699,29 +11699,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
@@ -11770,22 +11770,22 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11795,29 +11795,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
@@ -11839,17 +11839,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11859,29 +11859,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11891,14 +11891,14 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -11908,12 +11908,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11955,29 +11955,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
@@ -12026,7 +12026,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -12036,12 +12036,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12090,22 +12090,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12218,22 +12218,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12250,7 +12250,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -10793,7 +10793,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京昌平区首开Long街</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>首开Long街南区室外一层中庭</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京东城区国瑞城</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>国瑞城一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10872,7 +10872,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区首开Long街</t>
+          <t>小米汽车北京东城区国瑞城</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>首开Long街南区室外一层中庭</t>
+          <t>国瑞城一层中庭</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -11642,22 +11642,22 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11667,29 +11667,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
@@ -11711,17 +11711,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11731,29 +11731,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11763,29 +11763,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11795,29 +11795,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11827,29 +11827,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11859,29 +11859,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11891,29 +11891,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
@@ -12026,22 +12026,22 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12058,22 +12058,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12090,22 +12090,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12154,7 +12154,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12186,7 +12186,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12218,22 +12218,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12250,22 +12250,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -10857,7 +10857,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10872,7 +10872,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -11610,22 +11610,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
@@ -11647,17 +11647,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11667,29 +11667,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11699,29 +11699,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11763,29 +11763,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11795,29 +11795,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11827,29 +11827,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
@@ -11871,17 +11871,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11891,29 +11891,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11955,29 +11955,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
@@ -12026,7 +12026,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -12036,12 +12036,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12058,22 +12058,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12122,22 +12122,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12154,22 +12154,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12186,22 +12186,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12250,22 +12250,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
